--- a/week-09/NorthwindTablesAndColumns.xlsx
+++ b/week-09/NorthwindTablesAndColumns.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dahliasanchez\Documents\DataAnalytics\week-09\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12A5F50-177F-4EBB-B00C-476392388DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6886FF-4BD8-4BD9-AE7D-5FCE3AABDB91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{901F5D27-877F-4C94-89AE-9A9B6ECE5CB6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="141">
   <si>
     <t>table_name</t>
   </si>
@@ -316,39 +316,6 @@
     <t>N</t>
   </si>
   <si>
-    <t>Customer's Region</t>
-  </si>
-  <si>
-    <t>Customer's PostalCode</t>
-  </si>
-  <si>
-    <t>Customer's Country</t>
-  </si>
-  <si>
-    <t>Employee's LastName</t>
-  </si>
-  <si>
-    <t>Employee's FirstName</t>
-  </si>
-  <si>
-    <t>Employee's BirthDate</t>
-  </si>
-  <si>
-    <t>Employee's HireDate</t>
-  </si>
-  <si>
-    <t>Employee's Region</t>
-  </si>
-  <si>
-    <t>Employee's PostalCode</t>
-  </si>
-  <si>
-    <t>Employee's Country</t>
-  </si>
-  <si>
-    <t>Employee's ReportsTo</t>
-  </si>
-  <si>
     <t>Product ReorderLevel</t>
   </si>
   <si>
@@ -415,9 +382,6 @@
     <t xml:space="preserve">Company </t>
   </si>
   <si>
-    <t xml:space="preserve">Company Contact </t>
-  </si>
-  <si>
     <t>Shippers Company</t>
   </si>
   <si>
@@ -446,6 +410,54 @@
   </si>
   <si>
     <t>What does reorder level mean?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Contact </t>
+  </si>
+  <si>
+    <t>Customer City</t>
+  </si>
+  <si>
+    <t>Employee Title</t>
+  </si>
+  <si>
+    <t>Employee City</t>
+  </si>
+  <si>
+    <t>Employee Title Of Courtesy</t>
+  </si>
+  <si>
+    <t>Customer Region</t>
+  </si>
+  <si>
+    <t>Customer PostalCode</t>
+  </si>
+  <si>
+    <t>Customer Country</t>
+  </si>
+  <si>
+    <t>Employee Last Name</t>
+  </si>
+  <si>
+    <t>Employee First Name</t>
+  </si>
+  <si>
+    <t>Employee BirthDate</t>
+  </si>
+  <si>
+    <t>Employee HireDate</t>
+  </si>
+  <si>
+    <t>Employee Region</t>
+  </si>
+  <si>
+    <t>Employee PostalCode</t>
+  </si>
+  <si>
+    <t>Employee Country</t>
+  </si>
+  <si>
+    <t>Employee ReportsTo EmployeeID</t>
   </si>
 </sst>
 </file>
@@ -841,7 +853,7 @@
     <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.26953125" customWidth="1"/>
     <col min="7" max="7" width="17.81640625" customWidth="1"/>
-    <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.81640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.81640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.54296875" customWidth="1"/>
@@ -936,7 +948,7 @@
         <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="J3" t="s">
         <v>91</v>
@@ -945,7 +957,7 @@
         <v>92</v>
       </c>
       <c r="M3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -1031,7 +1043,7 @@
         <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="J7" t="s">
         <v>91</v>
@@ -1040,7 +1052,7 @@
         <v>92</v>
       </c>
       <c r="M7" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1063,7 +1075,7 @@
         <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J8" t="s">
         <v>92</v>
@@ -1092,7 +1104,7 @@
         <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J9" t="s">
         <v>92</v>
@@ -1138,7 +1150,10 @@
         <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="I11" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1161,7 +1176,7 @@
         <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="J12" t="s">
         <v>92</v>
@@ -1190,7 +1205,7 @@
         <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="J13" t="s">
         <v>92</v>
@@ -1219,7 +1234,7 @@
         <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="J14" t="s">
         <v>91</v>
@@ -1228,7 +1243,7 @@
         <v>92</v>
       </c>
       <c r="M14" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -1314,7 +1329,7 @@
         <v>91</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="J18" t="s">
         <v>91</v>
@@ -1323,7 +1338,7 @@
         <v>92</v>
       </c>
       <c r="N18" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -1346,7 +1361,7 @@
         <v>91</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="J19" t="s">
         <v>91</v>
@@ -1372,7 +1387,10 @@
         <v>60</v>
       </c>
       <c r="H20" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="I20" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -1392,7 +1410,10 @@
         <v>50</v>
       </c>
       <c r="H21" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="I21" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1415,7 +1436,7 @@
         <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="J22" t="s">
         <v>92</v>
@@ -1444,7 +1465,7 @@
         <v>91</v>
       </c>
       <c r="I23" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="J23" t="s">
         <v>91</v>
@@ -1490,7 +1511,10 @@
         <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="I25" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -1513,7 +1537,7 @@
         <v>91</v>
       </c>
       <c r="I26" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="J26" t="s">
         <v>92</v>
@@ -1542,7 +1566,7 @@
         <v>91</v>
       </c>
       <c r="I27" t="s">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="J27" t="s">
         <v>92</v>
@@ -1571,7 +1595,7 @@
         <v>91</v>
       </c>
       <c r="I28" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="J28" t="s">
         <v>91</v>
@@ -1580,7 +1604,7 @@
         <v>92</v>
       </c>
       <c r="M28" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -1683,7 +1707,7 @@
         <v>91</v>
       </c>
       <c r="I33" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="J33" t="s">
         <v>92</v>
@@ -1825,7 +1849,7 @@
         <v>91</v>
       </c>
       <c r="I39" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="J39" t="s">
         <v>91</v>
@@ -1834,10 +1858,10 @@
         <v>92</v>
       </c>
       <c r="L39" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="M39" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
@@ -1860,7 +1884,7 @@
         <v>91</v>
       </c>
       <c r="I40" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="J40" t="s">
         <v>91</v>
@@ -1869,7 +1893,7 @@
         <v>92</v>
       </c>
       <c r="M40" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
@@ -1892,7 +1916,7 @@
         <v>91</v>
       </c>
       <c r="I41" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="J41" t="s">
         <v>91</v>
@@ -1901,7 +1925,7 @@
         <v>92</v>
       </c>
       <c r="L41" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
@@ -1993,7 +2017,7 @@
         <v>91</v>
       </c>
       <c r="I45" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="J45" t="s">
         <v>92</v>
@@ -2022,7 +2046,7 @@
         <v>91</v>
       </c>
       <c r="I46" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="J46" t="s">
         <v>92</v>
@@ -2051,7 +2075,7 @@
         <v>91</v>
       </c>
       <c r="I47" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="J47" t="s">
         <v>92</v>
@@ -2123,7 +2147,7 @@
         <v>91</v>
       </c>
       <c r="I50" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="J50" t="s">
         <v>92</v>
@@ -2169,7 +2193,7 @@
         <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
@@ -2192,7 +2216,7 @@
         <v>91</v>
       </c>
       <c r="I53" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="J53" t="s">
         <v>92</v>
@@ -2221,7 +2245,7 @@
         <v>91</v>
       </c>
       <c r="I54" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="J54" t="s">
         <v>92</v>
@@ -2250,7 +2274,7 @@
         <v>91</v>
       </c>
       <c r="I55" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="J55" t="s">
         <v>91</v>
@@ -2259,7 +2283,7 @@
         <v>92</v>
       </c>
       <c r="M55" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
@@ -2305,7 +2329,7 @@
         <v>91</v>
       </c>
       <c r="I57" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="J57" t="s">
         <v>91</v>
@@ -2314,7 +2338,7 @@
         <v>92</v>
       </c>
       <c r="M57" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
@@ -2383,7 +2407,7 @@
         <v>91</v>
       </c>
       <c r="I60" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="J60" t="s">
         <v>91</v>
@@ -2412,7 +2436,7 @@
         <v>91</v>
       </c>
       <c r="I61" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="J61" t="s">
         <v>92</v>
@@ -2421,10 +2445,10 @@
         <v>91</v>
       </c>
       <c r="L61" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="M61" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
@@ -2447,16 +2471,16 @@
         <v>91</v>
       </c>
       <c r="I62" t="s">
+        <v>110</v>
+      </c>
+      <c r="J62" t="s">
+        <v>91</v>
+      </c>
+      <c r="K62" t="s">
+        <v>92</v>
+      </c>
+      <c r="M62" t="s">
         <v>121</v>
-      </c>
-      <c r="J62" t="s">
-        <v>91</v>
-      </c>
-      <c r="K62" t="s">
-        <v>92</v>
-      </c>
-      <c r="M62" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
@@ -2479,7 +2503,7 @@
         <v>91</v>
       </c>
       <c r="I63" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="J63" t="s">
         <v>91</v>
@@ -2508,7 +2532,7 @@
         <v>91</v>
       </c>
       <c r="I64" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="J64" t="s">
         <v>92</v>
@@ -2517,7 +2541,7 @@
         <v>91</v>
       </c>
       <c r="N64" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
@@ -2626,7 +2650,7 @@
         <v>91</v>
       </c>
       <c r="I69" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="J69" t="s">
         <v>92</v>
@@ -2698,7 +2722,7 @@
         <v>91</v>
       </c>
       <c r="I72" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="J72" t="s">
         <v>92</v>
@@ -2727,7 +2751,7 @@
         <v>91</v>
       </c>
       <c r="I73" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="J73" t="s">
         <v>92</v>
@@ -2756,7 +2780,7 @@
         <v>91</v>
       </c>
       <c r="I74" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="J74" t="s">
         <v>92</v>
@@ -2802,7 +2826,7 @@
         <v>30</v>
       </c>
       <c r="H76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.35">
@@ -2825,7 +2849,7 @@
         <v>91</v>
       </c>
       <c r="I77" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="J77" t="s">
         <v>92</v>
@@ -2854,7 +2878,7 @@
         <v>91</v>
       </c>
       <c r="I78" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="J78" t="s">
         <v>92</v>
@@ -2883,7 +2907,7 @@
         <v>91</v>
       </c>
       <c r="I79" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J79" t="s">
         <v>91</v>
@@ -2892,7 +2916,7 @@
         <v>92</v>
       </c>
       <c r="M79" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.35">
@@ -3027,6 +3051,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CA5D0A6329BB324E86983B32928CFC2E" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3d7eac4bce3bbb09c82bd908806be82e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xmlns:ns3="ced60a7f-99b1-48d2-b555-34851c8026ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eb51570e5b7cb8bd524bc2df5324d4a3" ns2:_="" ns3:_="">
     <xsd:import namespace="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
@@ -3267,25 +3310,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3296,6 +3320,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB560F9-4CC1-4243-8F16-7FDC2CD703FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
+    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA285021-94D7-4152-B2E7-B2D9504C2DBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3314,17 +3349,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BB560F9-4CC1-4243-8F16-7FDC2CD703FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0257D61C-6042-483B-9C34-3DE0D82CB154}">
   <ds:schemaRefs>
